--- a/data/trans_dic/P25A$voluntad-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,75; 91,79</t>
+          <t>41,96; 91,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,08; 100,0</t>
+          <t>64,63; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,59; 87,96</t>
+          <t>40,52; 87,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,6; 90,31</t>
+          <t>51,85; 90,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,92; 87,67</t>
+          <t>40,88; 87,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,94; 84,68</t>
+          <t>49,03; 85,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,75; 91,8</t>
+          <t>66,14; 91,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,24; 85,53</t>
+          <t>54,55; 88,67</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,21; 86,92</t>
+          <t>57,92; 85,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,96; 84,21</t>
+          <t>63,78; 84,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,51; 94,25</t>
+          <t>72,09; 93,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,81; 71,82</t>
+          <t>47,23; 71,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,1; 82,43</t>
+          <t>63,49; 81,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,72; 77,05</t>
+          <t>53,4; 78,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,15; 73,34</t>
+          <t>54,87; 73,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,36; 81,38</t>
+          <t>67,12; 81,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,26; 83,38</t>
+          <t>65,66; 82,84</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,34; 84,18</t>
+          <t>65,96; 84,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,9; 88,12</t>
+          <t>73,51; 87,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,87; 87,51</t>
+          <t>67,04; 86,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,24; 83,4</t>
+          <t>60,78; 82,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,13; 88,91</t>
+          <t>74,16; 88,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,87; 83,49</t>
+          <t>65,45; 83,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,93; 81,83</t>
+          <t>67,2; 81,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,53; 86,57</t>
+          <t>76,48; 86,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,18; 82,68</t>
+          <t>69,39; 83,04</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,83; 75,99</t>
+          <t>58,85; 75,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,35; 85,11</t>
+          <t>73,21; 84,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,68; 63,45</t>
+          <t>44,19; 64,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,05; 79,2</t>
+          <t>57,53; 81,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,19; 86,88</t>
+          <t>69,13; 86,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,1; 76,76</t>
+          <t>55,71; 76,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,13; 74,39</t>
+          <t>60,33; 74,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,64; 84,16</t>
+          <t>73,71; 84,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,43; 66,74</t>
+          <t>52,35; 67,23</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,36; 60,91</t>
+          <t>42,84; 60,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,72; 74,35</t>
+          <t>56,21; 72,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,01; 66,17</t>
+          <t>48,53; 65,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,26; 83,36</t>
+          <t>36,57; 82,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,92; 83,57</t>
+          <t>58,7; 84,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,45; 84,77</t>
+          <t>58,24; 84,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,51; 60,81</t>
+          <t>43,95; 60,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,34; 74,05</t>
+          <t>60,2; 74,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,66; 68,99</t>
+          <t>54,02; 68,75</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36,26; 54,47</t>
+          <t>35,7; 54,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48,92; 64,39</t>
+          <t>49,26; 65,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,55; 60,27</t>
+          <t>42,87; 60,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,36; 78,88</t>
+          <t>27,15; 79,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,98; 90,24</t>
+          <t>29,06; 90,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,14; 81,31</t>
+          <t>45,29; 83,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,85; 54,11</t>
+          <t>38,76; 55,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,7; 65,04</t>
+          <t>48,45; 65,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,46; 61,29</t>
+          <t>45,16; 61,89</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,18; 54,72</t>
+          <t>37,07; 55,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,95; 56,94</t>
+          <t>39,29; 56,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,78; 62,47</t>
+          <t>44,66; 62,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,54; 100,0</t>
+          <t>26,53; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,74; 100,0</t>
+          <t>36,58; 100,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,89; 56,42</t>
+          <t>38,67; 56,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,99; 57,96</t>
+          <t>40,87; 58,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,97; 63,93</t>
+          <t>45,71; 62,94</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,55; 61,28</t>
+          <t>53,56; 61,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,17; 70,85</t>
+          <t>63,84; 70,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56,39; 64,1</t>
+          <t>56,27; 64,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59,98; 72,58</t>
+          <t>60,04; 72,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>72,9; 81,84</t>
+          <t>72,97; 81,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,35; 74,91</t>
+          <t>64,57; 74,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,52; 63,28</t>
+          <t>56,57; 63,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>67,85; 73,29</t>
+          <t>67,77; 73,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60,47; 66,96</t>
+          <t>60,43; 66,62</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4826; 10362</t>
+          <t>4736; 10357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10085; 16785</t>
+          <t>10849; 16785</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1765,32 +1765,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6268; 13582</t>
+          <t>6257; 13561</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10307; 17365</t>
+          <t>9970; 17338</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6752; 14464</t>
+          <t>6745; 14481</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12547; 22637</t>
+          <t>13107; 22746</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24038; 33059</t>
+          <t>23820; 33100</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13813; 22193</t>
+          <t>14152; 23005</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22968; 34294</t>
+          <t>22853; 33916</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45797; 61247</t>
+          <t>46393; 61146</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35239; 45802</t>
+          <t>35032; 45480</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33497; 50321</t>
+          <t>33090; 50082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52290; 68303</t>
+          <t>52608; 67868</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30559; 44667</t>
+          <t>30953; 45414</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60403; 80317</t>
+          <t>60090; 80679</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>104803; 126625</t>
+          <t>104443; 126166</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70609; 88856</t>
+          <t>69968; 88279</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56354; 71517</t>
+          <t>56035; 71726</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83037; 99014</t>
+          <t>82595; 98561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50439; 65040</t>
+          <t>49822; 64543</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39919; 55264</t>
+          <t>40271; 54843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91988; 110327</t>
+          <t>92028; 110055</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57040; 73417</t>
+          <t>57551; 73189</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>101216; 123742</t>
+          <t>101623; 123279</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>180946; 204704</t>
+          <t>180850; 205478</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112249; 134149</t>
+          <t>112582; 134734</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73859; 95411</t>
+          <t>73887; 94403</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>122948; 144630</t>
+          <t>124412; 144322</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47257; 68647</t>
+          <t>47803; 69871</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33516; 46530</t>
+          <t>33796; 47592</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63373; 79570</t>
+          <t>63315; 79230</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49501; 67729</t>
+          <t>49150; 67157</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>110816; 137093</t>
+          <t>111195; 137449</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>192590; 220090</t>
+          <t>192758; 221420</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102981; 131096</t>
+          <t>102824; 132049</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55552; 78046</t>
+          <t>54887; 77164</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79542; 104274</t>
+          <t>78824; 102265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63853; 88009</t>
+          <t>64545; 87581</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6148; 14538</t>
+          <t>6377; 14421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29977; 43256</t>
+          <t>30381; 43860</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33838; 48249</t>
+          <t>33150; 47836</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64797; 88515</t>
+          <t>63968; 88395</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115850; 142178</t>
+          <t>115590; 142328</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>103813; 131022</t>
+          <t>102587; 130575</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44199; 66398</t>
+          <t>43513; 66007</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79523; 104664</t>
+          <t>80061; 106257</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52437; 74265</t>
+          <t>52821; 74884</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3705; 10682</t>
+          <t>3676; 10731</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3079; 9586</t>
+          <t>3087; 9571</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11114; 20948</t>
+          <t>11667; 21610</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51269; 73290</t>
+          <t>52497; 74849</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>86070; 112633</t>
+          <t>83895; 112814</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67723; 91320</t>
+          <t>67288; 92209</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42124; 61999</t>
+          <t>41999; 63146</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55112; 80563</t>
+          <t>55591; 79882</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48688; 67926</t>
+          <t>48556; 68032</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2635; 9234</t>
+          <t>2449; 9234</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2162; 6408</t>
+          <t>2344; 6408</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1075; 2495</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46424; 69139</t>
+          <t>47379; 68802</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>60619; 85712</t>
+          <t>60441; 86500</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>51131; 71101</t>
+          <t>50839; 70004</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>334485; 382759</t>
+          <t>334505; 382484</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>523706; 578177</t>
+          <t>520980; 577329</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>341428; 388135</t>
+          <t>340682; 387723</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>150391; 181985</t>
+          <t>150536; 181390</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>281802; 316349</t>
+          <t>282067; 314939</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>216088; 251543</t>
+          <t>216823; 250636</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>494708; 553869</t>
+          <t>495184; 552332</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>816026; 881413</t>
+          <t>815047; 880525</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>569218; 630305</t>
+          <t>568845; 627130</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$voluntad-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,96; 91,75</t>
+          <t>38,55; 92,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,63; 100,0</t>
+          <t>60,31; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,03; 100,0</t>
+          <t>56,42; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,52; 87,82</t>
+          <t>38,68; 86,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,85; 90,17</t>
+          <t>48,55; 89,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,88; 87,77</t>
+          <t>41,1; 87,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,03; 85,09</t>
+          <t>48,56; 85,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,14; 91,91</t>
+          <t>65,12; 91,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,55; 88,67</t>
+          <t>54,39; 88,67</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,92; 85,96</t>
+          <t>58,48; 87,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,78; 84,07</t>
+          <t>63,65; 84,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,09; 93,59</t>
+          <t>72,39; 94,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,23; 71,48</t>
+          <t>47,25; 71,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,49; 81,9</t>
+          <t>61,88; 82,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,4; 78,34</t>
+          <t>52,99; 76,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,87; 73,67</t>
+          <t>55,11; 73,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,12; 81,09</t>
+          <t>67,34; 80,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,66; 82,84</t>
+          <t>64,91; 83,14</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,96; 84,43</t>
+          <t>65,85; 85,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,51; 87,72</t>
+          <t>74,05; 88,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,04; 86,85</t>
+          <t>67,26; 87,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,78; 82,77</t>
+          <t>60,79; 84,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,16; 88,69</t>
+          <t>74,33; 88,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,45; 83,23</t>
+          <t>65,08; 83,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,2; 81,52</t>
+          <t>66,7; 81,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,48; 86,9</t>
+          <t>77,22; 86,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,39; 83,04</t>
+          <t>69,03; 83,2</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,85; 75,19</t>
+          <t>57,21; 75,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,21; 84,93</t>
+          <t>72,64; 85,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,19; 64,58</t>
+          <t>43,52; 63,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,53; 81,01</t>
+          <t>56,43; 79,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,13; 86,51</t>
+          <t>69,64; 87,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,71; 76,12</t>
+          <t>55,67; 75,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,33; 74,58</t>
+          <t>60,84; 74,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,71; 84,67</t>
+          <t>73,63; 84,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,35; 67,23</t>
+          <t>52,05; 66,59</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,84; 60,23</t>
+          <t>42,66; 60,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,21; 72,92</t>
+          <t>57,49; 74,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,53; 65,85</t>
+          <t>49,27; 65,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,57; 82,69</t>
+          <t>35,32; 82,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,7; 84,74</t>
+          <t>58,72; 84,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,24; 84,04</t>
+          <t>58,44; 83,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,95; 60,73</t>
+          <t>43,96; 60,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,2; 74,13</t>
+          <t>60,05; 74,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,02; 68,75</t>
+          <t>54,19; 68,98</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35,7; 54,15</t>
+          <t>36,47; 54,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49,26; 65,37</t>
+          <t>49,09; 65,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,87; 60,77</t>
+          <t>42,49; 60,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,15; 79,24</t>
+          <t>29,38; 79,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,06; 90,09</t>
+          <t>28,37; 90,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,29; 83,88</t>
+          <t>42,52; 80,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,76; 55,26</t>
+          <t>38,2; 55,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48,45; 65,15</t>
+          <t>49,69; 64,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,16; 61,89</t>
+          <t>45,58; 61,55</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1338,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,07; 55,73</t>
+          <t>36,79; 54,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,29; 56,46</t>
+          <t>38,57; 56,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,66; 62,57</t>
+          <t>44,45; 61,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,53; 100,0</t>
+          <t>27,42; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,58; 100,0</t>
+          <t>34,74; 100,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,67; 56,15</t>
+          <t>38,26; 56,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,87; 58,49</t>
+          <t>40,87; 57,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,71; 62,94</t>
+          <t>45,57; 62,96</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,56; 61,24</t>
+          <t>53,85; 61,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63,84; 70,74</t>
+          <t>63,91; 70,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56,27; 64,03</t>
+          <t>56,33; 63,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60,04; 72,34</t>
+          <t>60,06; 71,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>72,97; 81,47</t>
+          <t>73,32; 81,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,57; 74,64</t>
+          <t>65,07; 74,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,57; 63,1</t>
+          <t>56,47; 63,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>67,77; 73,22</t>
+          <t>67,98; 73,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60,43; 66,62</t>
+          <t>60,28; 66,77</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4736; 10357</t>
+          <t>4352; 10423</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10849; 16785</t>
+          <t>10123; 16785</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5293; 9447</t>
+          <t>5330; 9447</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6257; 13561</t>
+          <t>5974; 13402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9970; 17338</t>
+          <t>9336; 17247</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6745; 14481</t>
+          <t>6781; 14494</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13107; 22746</t>
+          <t>12980; 22758</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23820; 33100</t>
+          <t>23452; 33036</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14152; 23005</t>
+          <t>14111; 23007</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22853; 33916</t>
+          <t>23073; 34346</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46393; 61146</t>
+          <t>46293; 61296</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35032; 45480</t>
+          <t>35178; 45869</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33090; 50082</t>
+          <t>33105; 50137</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52608; 67868</t>
+          <t>51272; 68049</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30953; 45414</t>
+          <t>30719; 44532</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60090; 80679</t>
+          <t>60358; 80327</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>104443; 126166</t>
+          <t>104783; 125692</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69968; 88279</t>
+          <t>69169; 88597</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56035; 71726</t>
+          <t>55942; 72277</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82595; 98561</t>
+          <t>83198; 98885</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49822; 64543</t>
+          <t>49987; 64793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40271; 54843</t>
+          <t>40279; 55705</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92028; 110055</t>
+          <t>92235; 110163</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57551; 73189</t>
+          <t>57228; 73420</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>101623; 123279</t>
+          <t>100856; 123393</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>180850; 205478</t>
+          <t>182595; 204508</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112582; 134734</t>
+          <t>112007; 134994</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73887; 94403</t>
+          <t>71829; 94563</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>124412; 144322</t>
+          <t>123447; 144772</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47803; 69871</t>
+          <t>47085; 68386</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33796; 47592</t>
+          <t>33149; 46820</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63315; 79230</t>
+          <t>63777; 79917</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49150; 67157</t>
+          <t>49121; 66699</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>111195; 137449</t>
+          <t>112132; 138010</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>192758; 221420</t>
+          <t>192562; 220021</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102824; 132049</t>
+          <t>102239; 130795</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54887; 77164</t>
+          <t>54660; 77631</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78824; 102265</t>
+          <t>80627; 104655</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64545; 87581</t>
+          <t>65524; 87721</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6377; 14421</t>
+          <t>6160; 14397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30381; 43860</t>
+          <t>30391; 43579</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33150; 47836</t>
+          <t>33263; 47412</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63968; 88395</t>
+          <t>63994; 87752</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115590; 142328</t>
+          <t>115293; 142107</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>102587; 130575</t>
+          <t>102914; 131006</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43513; 66007</t>
+          <t>44453; 66221</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>80061; 106257</t>
+          <t>79796; 106746</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52821; 74884</t>
+          <t>52362; 74665</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3676; 10731</t>
+          <t>3979; 10719</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3087; 9571</t>
+          <t>3014; 9577</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11667; 21610</t>
+          <t>10955; 20791</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52497; 74849</t>
+          <t>51735; 74734</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83895; 112814</t>
+          <t>86048; 112430</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67288; 92209</t>
+          <t>67901; 91703</t>
         </is>
       </c>
     </row>
@@ -2728,27 +2728,27 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>41999; 63146</t>
+          <t>41688; 62075</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55591; 79882</t>
+          <t>54565; 80374</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48556; 68032</t>
+          <t>48324; 66873</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2449; 9234</t>
+          <t>2532; 9234</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2344; 6408</t>
+          <t>2226; 6408</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47379; 68802</t>
+          <t>46883; 68885</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>60441; 86500</t>
+          <t>60438; 85643</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50839; 70004</t>
+          <t>50680; 70023</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>334505; 382484</t>
+          <t>336313; 385026</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>520980; 577329</t>
+          <t>521546; 576324</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>340682; 387723</t>
+          <t>341105; 387069</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>150536; 181390</t>
+          <t>150598; 180176</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>282067; 314939</t>
+          <t>283419; 315071</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>216823; 250636</t>
+          <t>218497; 250987</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>495184; 552332</t>
+          <t>494299; 553554</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>815047; 880525</t>
+          <t>817611; 883544</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>568845; 627130</t>
+          <t>567445; 628504</t>
         </is>
       </c>
     </row>
